--- a/artfynd/A 48951-2022 artfynd.xlsx
+++ b/artfynd/A 48951-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48951-2022 artfynd.xlsx
+++ b/artfynd/A 48951-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112657524</v>
       </c>
       <c r="B2" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112657525</v>
+        <v>117992463</v>
       </c>
       <c r="B3" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storfall, Lögdeälven, Ång</t>
+          <t>Storfall, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707990</v>
+        <v>708144</v>
       </c>
       <c r="R3" t="n">
-        <v>7066594</v>
+        <v>7066393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,19 +861,310 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112657525</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storfall, Lögdeälven, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>707990</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7066593</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118462718</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storfall, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>708152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7066426</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117992462</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storfall, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>708144</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7066393</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hanna Bäckman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48951-2022 artfynd.xlsx
+++ b/artfynd/A 48951-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992463</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112657525</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462718</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,8 +1190,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992462</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>